--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84932475</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,8 +930,17 @@
           <t>Biogeografisk uppföljning av groddjur</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104340467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,10 +936,229 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136038943</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56713</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Flyeboda naturreservat, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552860</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6233147</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jämjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Isabel Vitaskär</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Isabel Vitaskär</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038943</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136039816</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102739</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Flyeboda naturreservat, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552928</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6232990</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jämjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isabel Vitaskär</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isabel Vitaskär</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136039816</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>136039816</v>
       </c>
       <c r="B5" t="n">
-        <v>102739</v>
+        <v>102740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>136039816</v>
       </c>
       <c r="B5" t="n">
-        <v>102740</v>
+        <v>102742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -1051,7 +1051,7 @@
         <v>136039816</v>
       </c>
       <c r="B5" t="n">
-        <v>102742</v>
+        <v>102743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -941,7 +941,7 @@
         <v>136038943</v>
       </c>
       <c r="B4" t="n">
-        <v>56713</v>
+        <v>56714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>136039816</v>
       </c>
       <c r="B5" t="n">
-        <v>102743</v>
+        <v>102744</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -941,7 +941,7 @@
         <v>136038943</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>56718</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>136039816</v>
       </c>
       <c r="B5" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27763-2024 artfynd.xlsx
+++ b/artfynd/A 27763-2024 artfynd.xlsx
@@ -941,7 +941,7 @@
         <v>136038943</v>
       </c>
       <c r="B4" t="n">
-        <v>56718</v>
+        <v>56719</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>136039816</v>
       </c>
       <c r="B5" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
